--- a/plugins/fire-service/skills/eptz/assets/smetka_template.xlsx
+++ b/plugins/fire-service/skills/eptz/assets/smetka_template.xlsx
@@ -189,7 +189,6 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
@@ -208,7 +207,6 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
@@ -290,7 +288,6 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
@@ -397,7 +394,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -410,7 +406,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
